--- a/HW1/result/HW_1.xlsx
+++ b/HW1/result/HW_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW1\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF68A81D-5565-4EC5-A2F1-BB6FF82837D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AC153B-ADE1-4F9E-85BA-6EF37EBDF4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8C4E29EA-1D70-4424-B9E1-A1A9A56CC44F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8C4E29EA-1D70-4424-B9E1-A1A9A56CC44F}"/>
   </bookViews>
   <sheets>
     <sheet name="HW Sensitivity Report 1" sheetId="2" r:id="rId1"/>
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -382,6 +382,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -391,9 +396,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1111,12 +1114,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1138,12 +1141,12 @@
       <c r="A5" s="4"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1165,30 +1168,30 @@
       <c r="A9" s="4"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="15">
         <f>SUMPRODUCT($A$4:$B$4,$A$8:$B$8)</f>
         <v>1740</v>
       </c>
-      <c r="D11" s="14"/>
+      <c r="D11" s="11"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
@@ -1230,12 +1233,12 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="11"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
@@ -1286,15 +1289,15 @@
       <c r="A23" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="10">
         <f>SUM(B21:B22)</f>
         <v>200</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="10">
         <f>SUM(C21:C22)</f>
         <v>112.00000000000001</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="10">
         <f>SUM(D21:D22)</f>
         <v>220</v>
       </c>
@@ -1303,13 +1306,13 @@
       <c r="A24" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="9">
         <v>200</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="9">
         <v>128</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="9">
         <f>220+50</f>
         <v>270</v>
       </c>
